--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117846153</v>
+        <v>117845484</v>
       </c>
       <c r="B2" t="n">
-        <v>90519</v>
+        <v>57534</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584856</v>
+        <v>584866</v>
       </c>
       <c r="R2" t="n">
-        <v>6427826</v>
+        <v>6427855</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,13 +765,17 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117846407</v>
+        <v>117845524</v>
       </c>
       <c r="B3" t="n">
         <v>97836</v>
@@ -833,14 +838,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584890</v>
+        <v>584893</v>
       </c>
       <c r="R3" t="n">
-        <v>6427785</v>
+        <v>6427827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117846446</v>
+        <v>117845427</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>104929</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +917,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -948,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584892</v>
+        <v>584939</v>
       </c>
       <c r="R4" t="n">
-        <v>6427806</v>
+        <v>6427824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117846284</v>
+        <v>117845690</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584868</v>
+        <v>584883</v>
       </c>
       <c r="R5" t="n">
-        <v>6427745</v>
+        <v>6427848</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117845690</v>
+        <v>117846407</v>
       </c>
       <c r="B6" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1155,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584883</v>
+        <v>584890</v>
       </c>
       <c r="R6" t="n">
-        <v>6427848</v>
+        <v>6427785</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1254,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117845794</v>
+        <v>117846446</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1284,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584831</v>
+        <v>584892</v>
       </c>
       <c r="R7" t="n">
-        <v>6427839</v>
+        <v>6427806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117845820</v>
+        <v>117845722</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1395,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584819</v>
+        <v>584860</v>
       </c>
       <c r="R8" t="n">
-        <v>6427842</v>
+        <v>6427838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1476,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117846119</v>
+        <v>117845857</v>
       </c>
       <c r="B9" t="n">
         <v>97836</v>
@@ -1506,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584831</v>
+        <v>584799</v>
       </c>
       <c r="R9" t="n">
-        <v>6427882</v>
+        <v>6427902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117845657</v>
+        <v>117846180</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1617,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584850</v>
+        <v>584862</v>
       </c>
       <c r="R10" t="n">
-        <v>6427848</v>
+        <v>6427833</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117845524</v>
+        <v>117846390</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1724,14 +1742,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584893</v>
+        <v>584908</v>
       </c>
       <c r="R11" t="n">
-        <v>6427827</v>
+        <v>6427759</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117846180</v>
+        <v>117845820</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1839,10 +1857,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584862</v>
+        <v>584819</v>
       </c>
       <c r="R12" t="n">
-        <v>6427833</v>
+        <v>6427842</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2013,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117845484</v>
+        <v>117845794</v>
       </c>
       <c r="B14" t="n">
-        <v>57534</v>
+        <v>97836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,39 +2043,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2065,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584866</v>
+        <v>584831</v>
       </c>
       <c r="R14" t="n">
-        <v>6427855</v>
+        <v>6427839</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,17 +2117,13 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2132,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117845427</v>
+        <v>117846153</v>
       </c>
       <c r="B15" t="n">
-        <v>104929</v>
+        <v>90519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,43 +2154,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2188,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584939</v>
+        <v>584856</v>
       </c>
       <c r="R15" t="n">
-        <v>6427824</v>
+        <v>6427826</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,11 +2229,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117845857</v>
+        <v>117846284</v>
       </c>
       <c r="B16" t="n">
         <v>97836</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584799</v>
+        <v>584868</v>
       </c>
       <c r="R16" t="n">
-        <v>6427902</v>
+        <v>6427745</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117846455</v>
+        <v>117846119</v>
       </c>
       <c r="B17" t="n">
         <v>97836</v>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584889</v>
+        <v>584831</v>
       </c>
       <c r="R17" t="n">
-        <v>6427802</v>
+        <v>6427882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117846390</v>
+        <v>117845620</v>
       </c>
       <c r="B18" t="n">
         <v>97836</v>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584908</v>
+        <v>584858</v>
       </c>
       <c r="R18" t="n">
-        <v>6427759</v>
+        <v>6427844</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117846433</v>
+        <v>117846249</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>94610</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,33 +2601,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2637,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584890</v>
+        <v>584843</v>
       </c>
       <c r="R19" t="n">
-        <v>6427780</v>
+        <v>6427762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2696,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117845722</v>
+        <v>117845657</v>
       </c>
       <c r="B20" t="n">
         <v>97836</v>
@@ -2748,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584860</v>
+        <v>584850</v>
       </c>
       <c r="R20" t="n">
-        <v>6427838</v>
+        <v>6427848</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2807,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117845620</v>
+        <v>117846433</v>
       </c>
       <c r="B21" t="n">
         <v>97836</v>
@@ -2859,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584858</v>
+        <v>584890</v>
       </c>
       <c r="R21" t="n">
-        <v>6427844</v>
+        <v>6427780</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117846249</v>
+        <v>117846517</v>
       </c>
       <c r="B22" t="n">
-        <v>94610</v>
+        <v>97836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,29 +2930,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584843</v>
+        <v>584951</v>
       </c>
       <c r="R22" t="n">
-        <v>6427762</v>
+        <v>6427822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117846359</v>
+        <v>117846455</v>
       </c>
       <c r="B23" t="n">
         <v>97836</v>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584894</v>
+        <v>584889</v>
       </c>
       <c r="R23" t="n">
-        <v>6427768</v>
+        <v>6427802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117846517</v>
+        <v>117846359</v>
       </c>
       <c r="B24" t="n">
         <v>97836</v>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584951</v>
+        <v>584894</v>
       </c>
       <c r="R24" t="n">
-        <v>6427822</v>
+        <v>6427768</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117845484</v>
+        <v>117846119</v>
       </c>
       <c r="B2" t="n">
-        <v>57534</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584866</v>
+        <v>584831</v>
       </c>
       <c r="R2" t="n">
-        <v>6427855</v>
+        <v>6427882</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,17 +761,13 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117845524</v>
+        <v>117845620</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584893</v>
+        <v>584858</v>
       </c>
       <c r="R3" t="n">
-        <v>6427827</v>
+        <v>6427844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117845427</v>
+        <v>117846455</v>
       </c>
       <c r="B4" t="n">
-        <v>104929</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,42 +909,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -961,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584939</v>
+        <v>584889</v>
       </c>
       <c r="R4" t="n">
-        <v>6427824</v>
+        <v>6427802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117845690</v>
+        <v>117846180</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584883</v>
+        <v>584862</v>
       </c>
       <c r="R5" t="n">
-        <v>6427848</v>
+        <v>6427833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117846407</v>
+        <v>117845820</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584890</v>
+        <v>584819</v>
       </c>
       <c r="R6" t="n">
-        <v>6427785</v>
+        <v>6427842</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117846446</v>
+        <v>117845722</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584892</v>
+        <v>584860</v>
       </c>
       <c r="R7" t="n">
-        <v>6427806</v>
+        <v>6427838</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117845722</v>
+        <v>117846407</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584860</v>
+        <v>584890</v>
       </c>
       <c r="R8" t="n">
-        <v>6427838</v>
+        <v>6427785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117845857</v>
+        <v>117846359</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584799</v>
+        <v>584894</v>
       </c>
       <c r="R9" t="n">
-        <v>6427902</v>
+        <v>6427768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117846180</v>
+        <v>117846390</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584862</v>
+        <v>584908</v>
       </c>
       <c r="R10" t="n">
-        <v>6427833</v>
+        <v>6427759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117846390</v>
+        <v>117846506</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584908</v>
+        <v>584903</v>
       </c>
       <c r="R11" t="n">
-        <v>6427759</v>
+        <v>6427800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117845820</v>
+        <v>117846433</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584819</v>
+        <v>584890</v>
       </c>
       <c r="R12" t="n">
-        <v>6427842</v>
+        <v>6427780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117846506</v>
+        <v>117845657</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584903</v>
+        <v>584850</v>
       </c>
       <c r="R13" t="n">
-        <v>6427800</v>
+        <v>6427848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117845794</v>
+        <v>117846517</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584831</v>
+        <v>584951</v>
       </c>
       <c r="R14" t="n">
-        <v>6427839</v>
+        <v>6427822</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117846153</v>
+        <v>117845524</v>
       </c>
       <c r="B15" t="n">
-        <v>90519</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,49 +2130,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584856</v>
+        <v>584893</v>
       </c>
       <c r="R15" t="n">
-        <v>6427826</v>
+        <v>6427827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117846284</v>
+        <v>117845484</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>57535</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,35 +2241,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2304,13 +2281,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584868</v>
+        <v>584866</v>
       </c>
       <c r="R16" t="n">
-        <v>6427745</v>
+        <v>6427855</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,13 +2319,17 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2367,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117846119</v>
+        <v>117846249</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>94612</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,33 +2360,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2415,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584831</v>
+        <v>584843</v>
       </c>
       <c r="R17" t="n">
-        <v>6427882</v>
+        <v>6427762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117845620</v>
+        <v>117845794</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584858</v>
+        <v>584831</v>
       </c>
       <c r="R18" t="n">
-        <v>6427844</v>
+        <v>6427839</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,10 +2566,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117846249</v>
+        <v>117845690</v>
       </c>
       <c r="B19" t="n">
-        <v>94610</v>
+        <v>90501</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,31 +2578,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2633,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584843</v>
+        <v>584883</v>
       </c>
       <c r="R19" t="n">
-        <v>6427762</v>
+        <v>6427848</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117845657</v>
+        <v>117845857</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584850</v>
+        <v>584799</v>
       </c>
       <c r="R20" t="n">
-        <v>6427848</v>
+        <v>6427902</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2807,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117846433</v>
+        <v>117846284</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584890</v>
+        <v>584868</v>
       </c>
       <c r="R21" t="n">
-        <v>6427780</v>
+        <v>6427745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2918,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117846517</v>
+        <v>117846153</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>90521</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2930,35 +2914,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2966,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584951</v>
+        <v>584856</v>
       </c>
       <c r="R22" t="n">
-        <v>6427822</v>
+        <v>6427826</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117846455</v>
+        <v>117845427</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>104931</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3041,34 +3028,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584889</v>
+        <v>584939</v>
       </c>
       <c r="R23" t="n">
-        <v>6427802</v>
+        <v>6427824</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,6 +3108,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117846359</v>
+        <v>117846446</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584894</v>
+        <v>584892</v>
       </c>
       <c r="R24" t="n">
-        <v>6427768</v>
+        <v>6427806</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
         <v>117854823</v>
       </c>
       <c r="B25" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117846153</v>
+        <v>117845427</v>
       </c>
       <c r="B22" t="n">
-        <v>90521</v>
+        <v>104931</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,38 +2914,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,10 +2958,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584856</v>
+        <v>584939</v>
       </c>
       <c r="R22" t="n">
-        <v>6427826</v>
+        <v>6427824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,6 +2994,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117845427</v>
+        <v>117846446</v>
       </c>
       <c r="B23" t="n">
-        <v>104931</v>
+        <v>97838</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,42 +3038,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3072,10 +3074,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584939</v>
+        <v>584892</v>
       </c>
       <c r="R23" t="n">
-        <v>6427824</v>
+        <v>6427806</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,11 +3110,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117846446</v>
+        <v>117846153</v>
       </c>
       <c r="B24" t="n">
-        <v>97838</v>
+        <v>90521</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3152,35 +3149,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584892</v>
+        <v>584856</v>
       </c>
       <c r="R24" t="n">
-        <v>6427806</v>
+        <v>6427826</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053647</v>
+        <v>120053813</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,49 +3377,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584814</v>
+        <v>584842</v>
       </c>
       <c r="R26" t="n">
-        <v>6427666</v>
+        <v>6427668</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053697</v>
+        <v>120053638</v>
       </c>
       <c r="B27" t="n">
-        <v>91836</v>
+        <v>90582</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,49 +3491,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584850</v>
+        <v>584799</v>
       </c>
       <c r="R27" t="n">
-        <v>6427689</v>
+        <v>6427665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053617</v>
+        <v>120053705</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>57316</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,35 +3605,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3638,13 +3645,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584825</v>
+        <v>584854</v>
       </c>
       <c r="R28" t="n">
-        <v>6427662</v>
+        <v>6427695</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3682,7 +3689,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3701,7 +3707,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053719</v>
+        <v>120053762</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3749,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584854</v>
+        <v>584864</v>
       </c>
       <c r="R29" t="n">
-        <v>6427691</v>
+        <v>6427684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,7 +3818,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053614</v>
+        <v>120053617</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3856,11 +3862,11 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584843</v>
+        <v>584825</v>
       </c>
       <c r="R30" t="n">
         <v>6427662</v>
@@ -3923,10 +3929,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053705</v>
+        <v>120053719</v>
       </c>
       <c r="B31" t="n">
-        <v>57316</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3935,39 +3941,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3978,10 +3980,10 @@
         <v>584854</v>
       </c>
       <c r="R31" t="n">
-        <v>6427695</v>
+        <v>6427691</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4019,6 +4021,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4037,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053762</v>
+        <v>120053697</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>91836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,35 +4052,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4085,10 +4091,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584864</v>
+        <v>584850</v>
       </c>
       <c r="R32" t="n">
-        <v>6427684</v>
+        <v>6427689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053813</v>
+        <v>120053647</v>
       </c>
       <c r="B33" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,52 +4166,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584842</v>
+        <v>584814</v>
       </c>
       <c r="R33" t="n">
-        <v>6427668</v>
+        <v>6427666</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4262,10 +4265,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053638</v>
+        <v>120053614</v>
       </c>
       <c r="B34" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4274,49 +4277,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584799</v>
+        <v>584843</v>
       </c>
       <c r="R34" t="n">
-        <v>6427665</v>
+        <v>6427662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053813</v>
+        <v>120053762</v>
       </c>
       <c r="B26" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,38 +3377,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3416,13 +3413,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584842</v>
+        <v>584864</v>
       </c>
       <c r="R26" t="n">
-        <v>6427668</v>
+        <v>6427684</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3479,7 +3476,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053638</v>
+        <v>120053813</v>
       </c>
       <c r="B27" t="n">
         <v>90582</v>
@@ -3526,17 +3523,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584799</v>
+        <v>584842</v>
       </c>
       <c r="R27" t="n">
-        <v>6427665</v>
+        <v>6427668</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3593,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053705</v>
+        <v>120053647</v>
       </c>
       <c r="B28" t="n">
-        <v>57316</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,53 +3602,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584854</v>
+        <v>584814</v>
       </c>
       <c r="R28" t="n">
-        <v>6427695</v>
+        <v>6427666</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3689,6 +3682,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3707,7 +3701,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053762</v>
+        <v>120053719</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3755,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584864</v>
+        <v>584854</v>
       </c>
       <c r="R29" t="n">
-        <v>6427684</v>
+        <v>6427691</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053617</v>
+        <v>120053697</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>91836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,35 +3824,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3866,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584825</v>
+        <v>584850</v>
       </c>
       <c r="R30" t="n">
-        <v>6427662</v>
+        <v>6427689</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3929,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053719</v>
+        <v>120053705</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>57316</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3941,35 +3938,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3980,10 +3981,10 @@
         <v>584854</v>
       </c>
       <c r="R31" t="n">
-        <v>6427691</v>
+        <v>6427695</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4021,7 +4022,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4040,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053697</v>
+        <v>120053638</v>
       </c>
       <c r="B32" t="n">
-        <v>91836</v>
+        <v>90582</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4052,49 +4052,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584850</v>
+        <v>584799</v>
       </c>
       <c r="R32" t="n">
-        <v>6427689</v>
+        <v>6427665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053647</v>
+        <v>120053617</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4198,14 +4198,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584814</v>
+        <v>584825</v>
       </c>
       <c r="R33" t="n">
-        <v>6427666</v>
+        <v>6427662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053762</v>
+        <v>120053705</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>57316</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,35 +3377,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3413,13 +3417,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584864</v>
+        <v>584854</v>
       </c>
       <c r="R26" t="n">
-        <v>6427684</v>
+        <v>6427695</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3457,7 +3461,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3476,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053813</v>
+        <v>120053617</v>
       </c>
       <c r="B27" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,38 +3491,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584842</v>
+        <v>584825</v>
       </c>
       <c r="R27" t="n">
-        <v>6427668</v>
+        <v>6427662</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053647</v>
+        <v>120053697</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,46 +3602,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584814</v>
+        <v>584850</v>
       </c>
       <c r="R28" t="n">
-        <v>6427666</v>
+        <v>6427689</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053719</v>
+        <v>120053813</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,35 +3716,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3749,13 +3755,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584854</v>
+        <v>584842</v>
       </c>
       <c r="R29" t="n">
-        <v>6427691</v>
+        <v>6427668</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3812,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053697</v>
+        <v>120053638</v>
       </c>
       <c r="B30" t="n">
-        <v>91836</v>
+        <v>90582</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,49 +3830,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584850</v>
+        <v>584799</v>
       </c>
       <c r="R30" t="n">
-        <v>6427689</v>
+        <v>6427665</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053705</v>
+        <v>120053762</v>
       </c>
       <c r="B31" t="n">
-        <v>57316</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,39 +3944,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3978,13 +3980,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584854</v>
+        <v>584864</v>
       </c>
       <c r="R31" t="n">
-        <v>6427695</v>
+        <v>6427684</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4022,6 +4024,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4040,10 +4043,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053638</v>
+        <v>120053614</v>
       </c>
       <c r="B32" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4052,49 +4055,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584799</v>
+        <v>584843</v>
       </c>
       <c r="R32" t="n">
-        <v>6427665</v>
+        <v>6427662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053617</v>
+        <v>120053719</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584825</v>
+        <v>584854</v>
       </c>
       <c r="R33" t="n">
-        <v>6427662</v>
+        <v>6427691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053614</v>
+        <v>120053647</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4309,14 +4309,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584843</v>
+        <v>584814</v>
       </c>
       <c r="R34" t="n">
-        <v>6427662</v>
+        <v>6427666</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -4043,7 +4043,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053614</v>
+        <v>120053719</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4087,14 +4087,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584843</v>
+        <v>584854</v>
       </c>
       <c r="R32" t="n">
-        <v>6427662</v>
+        <v>6427691</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053719</v>
+        <v>120053614</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4198,14 +4198,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584854</v>
+        <v>584843</v>
       </c>
       <c r="R33" t="n">
-        <v>6427691</v>
+        <v>6427662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -4043,7 +4043,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053719</v>
+        <v>120053614</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4087,14 +4087,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584854</v>
+        <v>584843</v>
       </c>
       <c r="R32" t="n">
-        <v>6427691</v>
+        <v>6427662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053614</v>
+        <v>120053719</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4198,14 +4198,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584843</v>
+        <v>584854</v>
       </c>
       <c r="R33" t="n">
-        <v>6427662</v>
+        <v>6427691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053705</v>
+        <v>120053762</v>
       </c>
       <c r="B26" t="n">
-        <v>57316</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,39 +3377,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3417,13 +3413,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584854</v>
+        <v>584864</v>
       </c>
       <c r="R26" t="n">
-        <v>6427695</v>
+        <v>6427684</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3461,6 +3457,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3479,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053617</v>
+        <v>120053813</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>90600</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,35 +3488,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584825</v>
+        <v>584842</v>
       </c>
       <c r="R27" t="n">
-        <v>6427662</v>
+        <v>6427668</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053697</v>
+        <v>120053617</v>
       </c>
       <c r="B28" t="n">
-        <v>91836</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,38 +3602,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3641,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584850</v>
+        <v>584825</v>
       </c>
       <c r="R28" t="n">
-        <v>6427689</v>
+        <v>6427662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053813</v>
+        <v>120053705</v>
       </c>
       <c r="B29" t="n">
-        <v>90582</v>
+        <v>57326</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,34 +3717,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3755,10 +3753,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584842</v>
+        <v>584854</v>
       </c>
       <c r="R29" t="n">
-        <v>6427668</v>
+        <v>6427695</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3799,7 +3797,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3821,7 +3818,7 @@
         <v>120053638</v>
       </c>
       <c r="B30" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3932,10 +3929,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053762</v>
+        <v>120053614</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3976,14 +3973,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584864</v>
+        <v>584843</v>
       </c>
       <c r="R31" t="n">
-        <v>6427684</v>
+        <v>6427662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4043,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053719</v>
+        <v>120053647</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4087,14 +4084,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584854</v>
+        <v>584814</v>
       </c>
       <c r="R32" t="n">
-        <v>6427691</v>
+        <v>6427666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053614</v>
+        <v>120053697</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>91854</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4166,46 +4163,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584843</v>
+        <v>584850</v>
       </c>
       <c r="R33" t="n">
-        <v>6427662</v>
+        <v>6427689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053647</v>
+        <v>120053719</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4309,14 +4309,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584814</v>
+        <v>584854</v>
       </c>
       <c r="R34" t="n">
-        <v>6427666</v>
+        <v>6427691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053762</v>
+        <v>120053638</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,46 +3377,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584864</v>
+        <v>584799</v>
       </c>
       <c r="R26" t="n">
-        <v>6427684</v>
+        <v>6427665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3476,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053813</v>
+        <v>120053617</v>
       </c>
       <c r="B27" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,38 +3491,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584842</v>
+        <v>584825</v>
       </c>
       <c r="R27" t="n">
-        <v>6427668</v>
+        <v>6427662</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053617</v>
+        <v>120053705</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>57326</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,35 +3602,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3638,13 +3642,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584825</v>
+        <v>584854</v>
       </c>
       <c r="R28" t="n">
-        <v>6427662</v>
+        <v>6427695</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3682,7 +3686,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3701,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053705</v>
+        <v>120053697</v>
       </c>
       <c r="B29" t="n">
-        <v>57326</v>
+        <v>91854</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,25 +3716,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100048</v>
+        <v>4363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3739,13 +3742,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3753,13 +3755,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584854</v>
+        <v>584850</v>
       </c>
       <c r="R29" t="n">
-        <v>6427695</v>
+        <v>6427689</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3797,6 +3799,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3815,7 +3818,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053638</v>
+        <v>120053813</v>
       </c>
       <c r="B30" t="n">
         <v>90600</v>
@@ -3862,17 +3865,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584799</v>
+        <v>584842</v>
       </c>
       <c r="R30" t="n">
-        <v>6427665</v>
+        <v>6427668</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053647</v>
+        <v>120053762</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -4084,14 +4087,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584814</v>
+        <v>584864</v>
       </c>
       <c r="R32" t="n">
-        <v>6427666</v>
+        <v>6427684</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4151,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053697</v>
+        <v>120053647</v>
       </c>
       <c r="B33" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,49 +4166,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584850</v>
+        <v>584814</v>
       </c>
       <c r="R33" t="n">
-        <v>6427689</v>
+        <v>6427666</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,7 +3365,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053638</v>
+        <v>120053813</v>
       </c>
       <c r="B26" t="n">
         <v>90600</v>
@@ -3412,17 +3412,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584799</v>
+        <v>584842</v>
       </c>
       <c r="R26" t="n">
-        <v>6427665</v>
+        <v>6427668</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053617</v>
+        <v>120053705</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>57326</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,35 +3491,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,13 +3531,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584825</v>
+        <v>584854</v>
       </c>
       <c r="R27" t="n">
-        <v>6427662</v>
+        <v>6427695</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3575,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3590,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053705</v>
+        <v>120053614</v>
       </c>
       <c r="B28" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,53 +3605,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584854</v>
+        <v>584843</v>
       </c>
       <c r="R28" t="n">
-        <v>6427695</v>
+        <v>6427662</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3686,6 +3685,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053697</v>
+        <v>120053647</v>
       </c>
       <c r="B29" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,49 +3716,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584850</v>
+        <v>584814</v>
       </c>
       <c r="R29" t="n">
-        <v>6427689</v>
+        <v>6427666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053813</v>
+        <v>120053762</v>
       </c>
       <c r="B30" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,38 +3827,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3869,13 +3863,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584842</v>
+        <v>584864</v>
       </c>
       <c r="R30" t="n">
-        <v>6427668</v>
+        <v>6427684</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3932,7 +3926,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053614</v>
+        <v>120053719</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3976,14 +3970,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584843</v>
+        <v>584854</v>
       </c>
       <c r="R31" t="n">
-        <v>6427662</v>
+        <v>6427691</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4043,10 +4037,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053762</v>
+        <v>120053697</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4055,35 +4049,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4091,10 +4088,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584864</v>
+        <v>584850</v>
       </c>
       <c r="R32" t="n">
-        <v>6427684</v>
+        <v>6427689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,7 +4151,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053647</v>
+        <v>120053617</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -4198,14 +4195,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584814</v>
+        <v>584825</v>
       </c>
       <c r="R33" t="n">
-        <v>6427666</v>
+        <v>6427662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4265,10 +4262,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053719</v>
+        <v>120053638</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4277,46 +4274,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584854</v>
+        <v>584799</v>
       </c>
       <c r="R34" t="n">
-        <v>6427691</v>
+        <v>6427665</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -4151,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053617</v>
+        <v>120053638</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,46 +4163,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584825</v>
+        <v>584799</v>
       </c>
       <c r="R33" t="n">
-        <v>6427662</v>
+        <v>6427665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4262,10 +4265,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053638</v>
+        <v>120053617</v>
       </c>
       <c r="B34" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4274,49 +4277,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584799</v>
+        <v>584825</v>
       </c>
       <c r="R34" t="n">
-        <v>6427665</v>
+        <v>6427662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053813</v>
+        <v>120053719</v>
       </c>
       <c r="B26" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,38 +3377,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3416,13 +3413,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584842</v>
+        <v>584854</v>
       </c>
       <c r="R26" t="n">
-        <v>6427668</v>
+        <v>6427691</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3479,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053705</v>
+        <v>120053617</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,39 +3488,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3531,13 +3524,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584854</v>
+        <v>584825</v>
       </c>
       <c r="R27" t="n">
-        <v>6427695</v>
+        <v>6427662</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3575,6 +3568,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3593,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053614</v>
+        <v>120053638</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,46 +3599,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584843</v>
+        <v>584799</v>
       </c>
       <c r="R28" t="n">
-        <v>6427662</v>
+        <v>6427665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,7 +3701,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053647</v>
+        <v>120053762</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3748,14 +3745,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584814</v>
+        <v>584864</v>
       </c>
       <c r="R29" t="n">
-        <v>6427666</v>
+        <v>6427684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053762</v>
+        <v>120053697</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,35 +3824,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584864</v>
+        <v>584850</v>
       </c>
       <c r="R30" t="n">
-        <v>6427684</v>
+        <v>6427689</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053719</v>
+        <v>120053647</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3970,14 +3970,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584854</v>
+        <v>584814</v>
       </c>
       <c r="R31" t="n">
-        <v>6427691</v>
+        <v>6427666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053697</v>
+        <v>120053614</v>
       </c>
       <c r="B32" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,49 +4049,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584850</v>
+        <v>584843</v>
       </c>
       <c r="R32" t="n">
-        <v>6427689</v>
+        <v>6427662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4151,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053638</v>
+        <v>120053705</v>
       </c>
       <c r="B33" t="n">
-        <v>90600</v>
+        <v>57326</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4167,48 +4164,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584799</v>
+        <v>584854</v>
       </c>
       <c r="R33" t="n">
-        <v>6427665</v>
+        <v>6427695</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4246,7 +4244,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4265,10 +4262,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053617</v>
+        <v>120053813</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4277,35 +4274,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584825</v>
+        <v>584842</v>
       </c>
       <c r="R34" t="n">
-        <v>6427662</v>
+        <v>6427668</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3476,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053617</v>
+        <v>120053705</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>57326</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,35 +3488,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3524,13 +3528,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584825</v>
+        <v>584854</v>
       </c>
       <c r="R27" t="n">
-        <v>6427662</v>
+        <v>6427695</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3572,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3587,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053638</v>
+        <v>120053762</v>
       </c>
       <c r="B28" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,49 +3602,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584799</v>
+        <v>584864</v>
       </c>
       <c r="R28" t="n">
-        <v>6427665</v>
+        <v>6427684</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053762</v>
+        <v>120053614</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3745,14 +3745,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584864</v>
+        <v>584843</v>
       </c>
       <c r="R29" t="n">
-        <v>6427684</v>
+        <v>6427662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053697</v>
+        <v>120053638</v>
       </c>
       <c r="B30" t="n">
-        <v>91854</v>
+        <v>90600</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,49 +3824,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584850</v>
+        <v>584799</v>
       </c>
       <c r="R30" t="n">
-        <v>6427689</v>
+        <v>6427665</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053614</v>
+        <v>120053813</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,49 +4049,52 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584843</v>
+        <v>584842</v>
       </c>
       <c r="R32" t="n">
-        <v>6427662</v>
+        <v>6427668</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4148,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053705</v>
+        <v>120053617</v>
       </c>
       <c r="B33" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,39 +4163,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4200,13 +4199,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584854</v>
+        <v>584825</v>
       </c>
       <c r="R33" t="n">
-        <v>6427695</v>
+        <v>6427662</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4244,6 +4243,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053813</v>
+        <v>120053697</v>
       </c>
       <c r="B34" t="n">
-        <v>90600</v>
+        <v>91854</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4274,35 +4274,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>4363</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584842</v>
+        <v>584850</v>
       </c>
       <c r="R34" t="n">
-        <v>6427668</v>
+        <v>6427689</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,7 +3365,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053719</v>
+        <v>120053614</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3409,14 +3409,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584854</v>
+        <v>584843</v>
       </c>
       <c r="R26" t="n">
-        <v>6427691</v>
+        <v>6427662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053705</v>
+        <v>120053697</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
+        <v>91854</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,25 +3488,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>4363</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3514,13 +3514,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3528,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584854</v>
+        <v>584850</v>
       </c>
       <c r="R27" t="n">
-        <v>6427695</v>
+        <v>6427689</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3572,6 +3571,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053762</v>
+        <v>120053647</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3634,14 +3634,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584864</v>
+        <v>584814</v>
       </c>
       <c r="R28" t="n">
-        <v>6427684</v>
+        <v>6427666</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120053614</v>
+        <v>120053638</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,46 +3713,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584843</v>
+        <v>584799</v>
       </c>
       <c r="R29" t="n">
-        <v>6427662</v>
+        <v>6427665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053638</v>
+        <v>120053762</v>
       </c>
       <c r="B30" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,49 +3827,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584799</v>
+        <v>584864</v>
       </c>
       <c r="R30" t="n">
-        <v>6427665</v>
+        <v>6427684</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053647</v>
+        <v>120053705</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>57326</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,49 +3938,53 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584814</v>
+        <v>584854</v>
       </c>
       <c r="R31" t="n">
-        <v>6427666</v>
+        <v>6427695</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4018,7 +4022,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4037,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053813</v>
+        <v>120053719</v>
       </c>
       <c r="B32" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,38 +4052,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4088,13 +4088,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584842</v>
+        <v>584854</v>
       </c>
       <c r="R32" t="n">
-        <v>6427668</v>
+        <v>6427691</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053617</v>
+        <v>120053813</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,35 +4163,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4199,13 +4202,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584825</v>
+        <v>584842</v>
       </c>
       <c r="R33" t="n">
-        <v>6427662</v>
+        <v>6427668</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4262,10 +4265,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053697</v>
+        <v>120053617</v>
       </c>
       <c r="B34" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4274,38 +4277,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584850</v>
+        <v>584825</v>
       </c>
       <c r="R34" t="n">
-        <v>6427689</v>
+        <v>6427662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20094-2024 artfynd.xlsx
+++ b/artfynd/A 20094-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120053614</v>
+        <v>120053697</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,46 +3377,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 20094, Sm</t>
+          <t>A 20094, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584843</v>
+        <v>584850</v>
       </c>
       <c r="R26" t="n">
-        <v>6427662</v>
+        <v>6427689</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3476,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120053697</v>
+        <v>120053813</v>
       </c>
       <c r="B27" t="n">
-        <v>91854</v>
+        <v>90600</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,35 +3491,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3527,13 +3530,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584850</v>
+        <v>584842</v>
       </c>
       <c r="R27" t="n">
-        <v>6427689</v>
+        <v>6427668</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120053647</v>
+        <v>120053614</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3634,14 +3637,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 39190, Härnum, Sm</t>
+          <t>A 20094, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584814</v>
+        <v>584843</v>
       </c>
       <c r="R28" t="n">
-        <v>6427666</v>
+        <v>6427662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3815,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120053762</v>
+        <v>120053705</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>57326</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,35 +3830,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3863,13 +3870,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584864</v>
+        <v>584854</v>
       </c>
       <c r="R30" t="n">
-        <v>6427684</v>
+        <v>6427695</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3907,7 +3914,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3926,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120053705</v>
+        <v>120053617</v>
       </c>
       <c r="B31" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,39 +3944,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3978,13 +3980,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584854</v>
+        <v>584825</v>
       </c>
       <c r="R31" t="n">
-        <v>6427695</v>
+        <v>6427662</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4022,6 +4024,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120053719</v>
+        <v>120053647</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -4084,14 +4087,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 20094, Härnum, Sm</t>
+          <t>A 39190, Härnum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584854</v>
+        <v>584814</v>
       </c>
       <c r="R32" t="n">
-        <v>6427691</v>
+        <v>6427666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4151,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120053813</v>
+        <v>120053762</v>
       </c>
       <c r="B33" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,38 +4166,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584842</v>
+        <v>584864</v>
       </c>
       <c r="R33" t="n">
-        <v>6427668</v>
+        <v>6427684</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120053617</v>
+        <v>120053719</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584825</v>
+        <v>584854</v>
       </c>
       <c r="R34" t="n">
-        <v>6427662</v>
+        <v>6427691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
